--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,13 +52,67 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-09T04:31:12.153Z</t>
+    <t>2026-10-11T02:47:07.677Z</t>
   </si>
   <si>
     <t>Blue Water Finance - Offering Superior Consumer Financing and Insurance services for Boat Dealers</t>
   </si>
   <si>
     <t>https://bluewaterfinance.com/</t>
+  </si>
+  <si>
+    <t>insurance.report.json</t>
+  </si>
+  <si>
+    <t>["hero-caption","columns-cta","columns-logos"]</t>
+  </si>
+  <si>
+    <t>insurance</t>
+  </si>
+  <si>
+    <t>content-page</t>
+  </si>
+  <si>
+    <t>2026-10-11T02:46:21.486Z</t>
+  </si>
+  <si>
+    <t>Offer The Right Boat Insurance At The Right Price | Blue Water Finance</t>
+  </si>
+  <si>
+    <t>https://bluewaterfinance.com/insurance/</t>
+  </si>
+  <si>
+    <t>loans.report.json</t>
+  </si>
+  <si>
+    <t>loans</t>
+  </si>
+  <si>
+    <t>2026-10-11T02:46:10.739Z</t>
+  </si>
+  <si>
+    <t>Get More Deals Done With Expert Boat Financing | Blue Water Finance</t>
+  </si>
+  <si>
+    <t>https://bluewaterfinance.com/loans/</t>
+  </si>
+  <si>
+    <t>protection.report.json</t>
+  </si>
+  <si>
+    <t>["hero-caption","accordion-boxed","columns-cta","columns-logos"]</t>
+  </si>
+  <si>
+    <t>protection</t>
+  </si>
+  <si>
+    <t>2026-10-11T02:46:16.711Z</t>
+  </si>
+  <si>
+    <t>Protect Your Customers With Leading Product Protection | Blue Water Finance</t>
+  </si>
+  <si>
+    <t>https://bluewaterfinance.com/protection/</t>
   </si>
 </sst>
 </file>
@@ -447,16 +501,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="31" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +563,84 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,48 @@
     <t>url</t>
   </si>
   <si>
+    <t>apply.report.json</t>
+  </si>
+  <si>
+    <t>["hero-caption","columns-cta","columns-logos"]</t>
+  </si>
+  <si>
+    <t>apply</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>content-page</t>
+  </si>
+  <si>
+    <t>2026-10-11T04:53:42.316Z</t>
+  </si>
+  <si>
+    <t>Offer Buyers The Boat They Really Want With Easy Financing | Blue Water Finance</t>
+  </si>
+  <si>
+    <t>https://bluewaterfinance.com/apply/</t>
+  </si>
+  <si>
+    <t>dealer-tools.report.json</t>
+  </si>
+  <si>
+    <t>["hero-caption","accordion-boxed","columns-cta","columns-logos"]</t>
+  </si>
+  <si>
+    <t>dealer-tools</t>
+  </si>
+  <si>
+    <t>2026-10-11T04:53:46.765Z</t>
+  </si>
+  <si>
+    <t>Access Useful Information For Getting Deals Done | Blue Water Finance</t>
+  </si>
+  <si>
+    <t>https://bluewaterfinance.com/dealer-tools/</t>
+  </si>
+  <si>
     <t>index.report.json</t>
   </si>
   <si>
@@ -46,13 +88,10 @@
     <t>index</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-11T02:47:07.677Z</t>
+    <t>2026-10-11T05:28:49.075Z</t>
   </si>
   <si>
     <t>Blue Water Finance - Offering Superior Consumer Financing and Insurance services for Boat Dealers</t>
@@ -64,16 +103,10 @@
     <t>insurance.report.json</t>
   </si>
   <si>
-    <t>["hero-caption","columns-cta","columns-logos"]</t>
-  </si>
-  <si>
     <t>insurance</t>
   </si>
   <si>
-    <t>content-page</t>
-  </si>
-  <si>
-    <t>2026-10-11T02:46:21.486Z</t>
+    <t>2026-10-11T04:44:29.048Z</t>
   </si>
   <si>
     <t>Offer The Right Boat Insurance At The Right Price | Blue Water Finance</t>
@@ -88,7 +121,7 @@
     <t>loans</t>
   </si>
   <si>
-    <t>2026-10-11T02:46:10.739Z</t>
+    <t>2026-10-11T04:44:18.154Z</t>
   </si>
   <si>
     <t>Get More Deals Done With Expert Boat Financing | Blue Water Finance</t>
@@ -97,16 +130,28 @@
     <t>https://bluewaterfinance.com/loans/</t>
   </si>
   <si>
+    <t>prequalify.report.json</t>
+  </si>
+  <si>
+    <t>prequalify</t>
+  </si>
+  <si>
+    <t>2026-10-11T04:53:36.785Z</t>
+  </si>
+  <si>
+    <t>Find Out What Size Boat Your Customers Can Afford | Blue Water Finance</t>
+  </si>
+  <si>
+    <t>https://bluewaterfinance.com/prequalify/</t>
+  </si>
+  <si>
     <t>protection.report.json</t>
   </si>
   <si>
-    <t>["hero-caption","accordion-boxed","columns-cta","columns-logos"]</t>
-  </si>
-  <si>
     <t>protection</t>
   </si>
   <si>
-    <t>2026-10-11T02:46:16.711Z</t>
+    <t>2026-10-11T04:44:22.948Z</t>
   </si>
   <si>
     <t>Protect Your Customers With Leading Product Protection | Blue Water Finance</t>
@@ -501,16 +546,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="42" customWidth="1"/>
+    <col min="8" max="8" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -579,24 +624,24 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>24</v>
@@ -605,24 +650,24 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
         <v>30</v>
@@ -631,7 +676,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
@@ -641,6 +686,84 @@
       </c>
       <c r="H5" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
